--- a/XBRL-template-MPERS/backup-originals/Company/04-SOPL-Nature.xlsx
+++ b/XBRL-template-MPERS/backup-originals/Company/04-SOPL-Nature.xlsx
@@ -644,10 +644,18 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Profit (loss)</t>
-        </is>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>*Profit (loss)</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>1*B25+1*B27</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>1*C25+1*C27</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -685,11 +693,11 @@
         </is>
       </c>
       <c r="B33">
-        <f>1*B25+1*B30+1*B27+1*B31+1*B32</f>
+        <f>1*B30+1*B31+1*B32</f>
         <v/>
       </c>
       <c r="C33">
-        <f>1*C25+1*C30+1*C27+1*C31+1*C32</f>
+        <f>1*C30+1*C31+1*C32</f>
         <v/>
       </c>
     </row>
@@ -1524,11 +1532,11 @@
         </is>
       </c>
       <c r="B104">
-        <f>1*B102+1*B102+1*B103+1*B103</f>
+        <f>1*B102+1*B103</f>
         <v/>
       </c>
       <c r="C104">
-        <f>1*C102+1*C102+1*C103+1*C103</f>
+        <f>1*C102+1*C103</f>
         <v/>
       </c>
     </row>
@@ -1588,11 +1596,11 @@
         </is>
       </c>
       <c r="B112">
-        <f>1*B109+1*B109+1*B110+1*B110+1*B111+1*B111</f>
+        <f>1*B109+1*B110+1*B111</f>
         <v/>
       </c>
       <c r="C112">
-        <f>1*C109+1*C109+1*C110+1*C110+1*C111+1*C111</f>
+        <f>1*C109+1*C110+1*C111</f>
         <v/>
       </c>
     </row>
@@ -1729,11 +1737,11 @@
         </is>
       </c>
       <c r="B131">
-        <f>1*B122+1*B122+1*B123+1*B123+1*B124+1*B124+1*B125+1*B125+1*B126+1*B126+1*B127+1*B127+1*B129+1*B129+1*B128+1*B128+1*B130+1*B130</f>
+        <f>1*B122+1*B123+1*B124+1*B125+1*B126+1*B127+1*B129+1*B128+1*B130</f>
         <v/>
       </c>
       <c r="C131">
-        <f>1*C122+1*C122+1*C123+1*C123+1*C124+1*C124+1*C125+1*C125+1*C126+1*C126+1*C127+1*C127+1*C129+1*C129+1*C128+1*C128+1*C130+1*C130</f>
+        <f>1*C122+1*C123+1*C124+1*C125+1*C126+1*C127+1*C129+1*C128+1*C130</f>
         <v/>
       </c>
     </row>
